--- a/data/Diessenhofen/cost/cost_report.xlsx
+++ b/data/Diessenhofen/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>743.0225112398958</v>
+        <v>631.4269318890211</v>
       </c>
       <c r="C2" t="n">
-        <v>27302.84343756951</v>
+        <v>25517.8117441478</v>
       </c>
       <c r="D2" t="n">
-        <v>-29848.20343238752</v>
+        <v>-20046.72688484902</v>
       </c>
       <c r="E2" t="n">
-        <v>2696.22387101199</v>
+        <v>2652.628781393783</v>
       </c>
       <c r="F2" t="n">
-        <v>50057.40742454031</v>
+        <v>45954.02920869345</v>
       </c>
       <c r="G2" t="n">
-        <v>50951.29381197419</v>
+        <v>54709.16978127504</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.08982333093242385</v>
+        <v>2.314756463898112</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>743.8949434185173</v>
+        <v>639.5386978914028</v>
       </c>
       <c r="C3" t="n">
-        <v>27167.21839706845</v>
+        <v>25454.52700270381</v>
       </c>
       <c r="D3" t="n">
-        <v>-29688.63754271872</v>
+        <v>-19889.61481335866</v>
       </c>
       <c r="E3" t="n">
-        <v>2708.593693903461</v>
+        <v>2656.952695354621</v>
       </c>
       <c r="F3" t="n">
-        <v>50749.46540455339</v>
+        <v>46564.47508247336</v>
       </c>
       <c r="G3" t="n">
-        <v>51680.53489622509</v>
+        <v>55425.87866506453</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.09110892857557526</v>
+        <v>2.345080567300112</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>751.4572040799621</v>
+        <v>635.2298305250218</v>
       </c>
       <c r="C4" t="n">
-        <v>7413.153782687526</v>
+        <v>7580.115918166738</v>
       </c>
       <c r="D4" t="n">
-        <v>39281.25295657184</v>
+        <v>43479.79370267048</v>
       </c>
       <c r="E4" t="n">
-        <v>2672.853124939613</v>
+        <v>2588.573651647478</v>
       </c>
       <c r="F4" t="n">
-        <v>21334.17309043259</v>
+        <v>18644.89609090676</v>
       </c>
       <c r="G4" t="n">
-        <v>71452.89015871153</v>
+        <v>72928.60919391649</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1259661162381658</v>
+        <v>3.08562477203768</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>751.3145807957259</v>
+        <v>637.7092174909773</v>
       </c>
       <c r="C5" t="n">
-        <v>7497.967742654228</v>
+        <v>7459.394986167554</v>
       </c>
       <c r="D5" t="n">
-        <v>39783.13325887209</v>
+        <v>42990.55871381954</v>
       </c>
       <c r="E5" t="n">
-        <v>2581.560897699063</v>
+        <v>2586.148099018714</v>
       </c>
       <c r="F5" t="n">
-        <v>20120.04766558845</v>
+        <v>19964.9305572039</v>
       </c>
       <c r="G5" t="n">
-        <v>70734.02414560955</v>
+        <v>73638.74157370068</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1246988090716546</v>
+        <v>3.115670622173965</v>
       </c>
     </row>
   </sheetData>
